--- a/datasets/election_data/data/output/ie_parties.xlsx
+++ b/datasets/election_data/data/output/ie_parties.xlsx
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Midlands–North-West</t>
+          <t>Midlands-North-West</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
